--- a/ci-cd-merge-resolver/repoCollector/datasets/rocketmq.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/rocketmq.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="69">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -44,6 +44,15 @@
     <t>isMultiModule</t>
   </si>
   <si>
+    <t>1483d679d7f41becfe45420cf189c627aa625851</t>
+  </si>
+  <si>
+    <t>773e1ac1962a826324c47752b89ab22e75cdc34c</t>
+  </si>
+  <si>
+    <t>e976cdbfc12b0088d95139c7136fee203647cedf</t>
+  </si>
+  <si>
     <t>9fbaced20f5aac042362aa4088accd677d86844c</t>
   </si>
   <si>
@@ -53,13 +62,115 @@
     <t>b136f9bb6725867dcc5d00798addd0de7382ffb3</t>
   </si>
   <si>
-    <t>1483d679d7f41becfe45420cf189c627aa625851</t>
-  </si>
-  <si>
-    <t>773e1ac1962a826324c47752b89ab22e75cdc34c</t>
-  </si>
-  <si>
-    <t>e976cdbfc12b0088d95139c7136fee203647cedf</t>
+    <t>f51f9f657fdb5cc582a891d5c7d17247f061de3a</t>
+  </si>
+  <si>
+    <t>973359f2e6973d63d420b32d5a463ee53319f838</t>
+  </si>
+  <si>
+    <t>f751fc313cf284dfe98bc1bbcb1781149c9157c6</t>
+  </si>
+  <si>
+    <t>3fadc8f30c898f9ddd6730ba4ac428894a1c1077</t>
+  </si>
+  <si>
+    <t>418a5b2eaf746735d9b9c8b7b3759ec3aa096f31</t>
+  </si>
+  <si>
+    <t>ef37465e593a06fdef4eb74b539a4146a4d4839c</t>
+  </si>
+  <si>
+    <t>fcdbc30233beea2dede33e710cef3d01bfe7a0cf</t>
+  </si>
+  <si>
+    <t>8f99df33ba37c8a6ae8de7a6f552fcb2b4f9c73b</t>
+  </si>
+  <si>
+    <t>8ccffa7e8ad3fcc30c3390591118b86b0f5be897</t>
+  </si>
+  <si>
+    <t>2c68a0e89fa8e49c48bcd41a5fd17b84b1be41f2</t>
+  </si>
+  <si>
+    <t>06c8b2b9b0302573c0df382a03ee6c9eda683c38</t>
+  </si>
+  <si>
+    <t>1905756db2c2c7bae1856595b6476bfee3f7b619</t>
+  </si>
+  <si>
+    <t>d21266d98822ade56c2b2420fc8d96df28a0eafe</t>
+  </si>
+  <si>
+    <t>3aa4943776b86b459bf0fee4aec50f31c6b05e62</t>
+  </si>
+  <si>
+    <t>d067bfc21410c11dc3c99bb2b67403aa4b344286</t>
+  </si>
+  <si>
+    <t>541a6d0124ce749197b381459b2542c0301bfaff</t>
+  </si>
+  <si>
+    <t>911ee340cb502645cd75603f44ba72c198611434</t>
+  </si>
+  <si>
+    <t>a4cccea9db284e92812b2c9f17043a8b4ce589d8</t>
+  </si>
+  <si>
+    <t>dde98ac2caacb22974723f83d157509013a95a21</t>
+  </si>
+  <si>
+    <t>c3a3334e84f9aa3dff288fe0ca7360370432f7ab</t>
+  </si>
+  <si>
+    <t>e656a8efab2bad6546c375c5527cda6585599423</t>
+  </si>
+  <si>
+    <t>3cd0ec9a8349a3a89a135b581ed1b2e2bc10a167</t>
+  </si>
+  <si>
+    <t>302de8b795215c350f2c61f9f02698dac015ba58</t>
+  </si>
+  <si>
+    <t>251fc77957b876f4cbf2ca516a944612ef1391a2</t>
+  </si>
+  <si>
+    <t>ac82378aeaa1717729f5262c2b573226b513a265</t>
+  </si>
+  <si>
+    <t>7e6bee2c48234d3785e31826a5589e3910738d4d</t>
+  </si>
+  <si>
+    <t>48fa70bc8c3f55ca70b879f69110923977ef2fbb</t>
+  </si>
+  <si>
+    <t>d98192b29dd08670375e516b8681f8576589206a</t>
+  </si>
+  <si>
+    <t>df1d93fc8859377b92ba87c6947911281656f355</t>
+  </si>
+  <si>
+    <t>a44699acd6eafe09e8d78d5c9fecded62134dcdf</t>
+  </si>
+  <si>
+    <t>8fc952d20c5b265e2d652fb556999a8e9f8df1a8</t>
+  </si>
+  <si>
+    <t>4f48fb74dc2fcb389710653148ba4c08fe00205d</t>
+  </si>
+  <si>
+    <t>7b7e45bca15500e3f36940180c87f80ceab291eb</t>
+  </si>
+  <si>
+    <t>b219c161b78be6d9c0a7877c914ea81c720e1d12</t>
+  </si>
+  <si>
+    <t>4f3389573428d872f282fad002fa5e8308d9d4b2</t>
+  </si>
+  <si>
+    <t>b186bcd53f7f211a6557d5121ffd4a7afdfc93bb</t>
+  </si>
+  <si>
+    <t>cca4d9239915f23da079b5a6b1ba5a47e6117945</t>
   </si>
   <si>
     <t>e84221d6089ccb3fffb5e3a223935d3bf26f811e</t>
@@ -71,100 +182,16 @@
     <t>5d212571f53c57d2ef1c81c76d6ba466a2d7d703</t>
   </si>
   <si>
-    <t>2c68a0e89fa8e49c48bcd41a5fd17b84b1be41f2</t>
-  </si>
-  <si>
-    <t>06c8b2b9b0302573c0df382a03ee6c9eda683c38</t>
-  </si>
-  <si>
-    <t>1905756db2c2c7bae1856595b6476bfee3f7b619</t>
-  </si>
-  <si>
-    <t>d21266d98822ade56c2b2420fc8d96df28a0eafe</t>
-  </si>
-  <si>
-    <t>3aa4943776b86b459bf0fee4aec50f31c6b05e62</t>
-  </si>
-  <si>
-    <t>d067bfc21410c11dc3c99bb2b67403aa4b344286</t>
-  </si>
-  <si>
-    <t>48fa70bc8c3f55ca70b879f69110923977ef2fbb</t>
-  </si>
-  <si>
-    <t>d98192b29dd08670375e516b8681f8576589206a</t>
-  </si>
-  <si>
-    <t>df1d93fc8859377b92ba87c6947911281656f355</t>
-  </si>
-  <si>
-    <t>e656a8efab2bad6546c375c5527cda6585599423</t>
-  </si>
-  <si>
-    <t>3cd0ec9a8349a3a89a135b581ed1b2e2bc10a167</t>
-  </si>
-  <si>
-    <t>302de8b795215c350f2c61f9f02698dac015ba58</t>
-  </si>
-  <si>
-    <t>4f3389573428d872f282fad002fa5e8308d9d4b2</t>
-  </si>
-  <si>
-    <t>b186bcd53f7f211a6557d5121ffd4a7afdfc93bb</t>
-  </si>
-  <si>
-    <t>cca4d9239915f23da079b5a6b1ba5a47e6117945</t>
-  </si>
-  <si>
-    <t>4f48fb74dc2fcb389710653148ba4c08fe00205d</t>
-  </si>
-  <si>
-    <t>7b7e45bca15500e3f36940180c87f80ceab291eb</t>
-  </si>
-  <si>
-    <t>b219c161b78be6d9c0a7877c914ea81c720e1d12</t>
-  </si>
-  <si>
-    <t>fcdbc30233beea2dede33e710cef3d01bfe7a0cf</t>
-  </si>
-  <si>
-    <t>8f99df33ba37c8a6ae8de7a6f552fcb2b4f9c73b</t>
-  </si>
-  <si>
-    <t>8ccffa7e8ad3fcc30c3390591118b86b0f5be897</t>
-  </si>
-  <si>
-    <t>541a6d0124ce749197b381459b2542c0301bfaff</t>
-  </si>
-  <si>
-    <t>911ee340cb502645cd75603f44ba72c198611434</t>
-  </si>
-  <si>
-    <t>a4cccea9db284e92812b2c9f17043a8b4ce589d8</t>
-  </si>
-  <si>
-    <t>a44699acd6eafe09e8d78d5c9fecded62134dcdf</t>
-  </si>
-  <si>
-    <t>8fc952d20c5b265e2d652fb556999a8e9f8df1a8</t>
-  </si>
-  <si>
-    <t>3fadc8f30c898f9ddd6730ba4ac428894a1c1077</t>
-  </si>
-  <si>
-    <t>418a5b2eaf746735d9b9c8b7b3759ec3aa096f31</t>
-  </si>
-  <si>
-    <t>ef37465e593a06fdef4eb74b539a4146a4d4839c</t>
-  </si>
-  <si>
-    <t>f51f9f657fdb5cc582a891d5c7d17247f061de3a</t>
-  </si>
-  <si>
-    <t>973359f2e6973d63d420b32d5a463ee53319f838</t>
-  </si>
-  <si>
-    <t>f751fc313cf284dfe98bc1bbcb1781149c9157c6</t>
+    <t>6ff00ed0530bbd94e6ed9cc444b0a2fdb57c7ba3</t>
+  </si>
+  <si>
+    <t>505cb2af9b9b64df7bb661779e03b6f250a3c12f</t>
+  </si>
+  <si>
+    <t>1b77be4d28bd2d25570dc350c0f4f727f0c8a3eb</t>
+  </si>
+  <si>
+    <t>05fee0d773d971cc56aafbbb95955f44fb963bed</t>
   </si>
   <si>
     <t>f1b0318d1a6c1e8417a5a779f4219ffddd418001</t>
@@ -185,12 +212,6 @@
     <t>1e8e72825932e2bbba459800f075b468e50d762f</t>
   </si>
   <si>
-    <t>dde98ac2caacb22974723f83d157509013a95a21</t>
-  </si>
-  <si>
-    <t>c3a3334e84f9aa3dff288fe0ca7360370432f7ab</t>
-  </si>
-  <si>
     <t>3aa31a6a36d70be025a4a84c4fdd8084708b35f5</t>
   </si>
   <si>
@@ -198,18 +219,6 @@
   </si>
   <si>
     <t>40d950578643775000ba29a33afdc3d8746cb8b6</t>
-  </si>
-  <si>
-    <t>6ff00ed0530bbd94e6ed9cc444b0a2fdb57c7ba3</t>
-  </si>
-  <si>
-    <t>505cb2af9b9b64df7bb661779e03b6f250a3c12f</t>
-  </si>
-  <si>
-    <t>1b77be4d28bd2d25570dc350c0f4f727f0c8a3eb</t>
-  </si>
-  <si>
-    <t>05fee0d773d971cc56aafbbb95955f44fb963bed</t>
   </si>
 </sst>
 </file>
@@ -254,7 +263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -300,13 +309,13 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>18.0</v>
+        <v>12.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
       <c r="G2" t="b" s="0">
         <v>0</v>
@@ -315,10 +324,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>0.6740000247955322</v>
+        <v>0.5799999833106995</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -332,13 +341,13 @@
         <v>15</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="G3" t="b" s="0">
         <v>0</v>
@@ -347,10 +356,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>1.8870000839233398</v>
+        <v>1.121000051498413</v>
       </c>
       <c r="J3" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -364,13 +373,13 @@
         <v>18</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>27.0</v>
+        <v>21.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G4" t="b" s="0">
         <v>0</v>
@@ -379,10 +388,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>6.726999282836914</v>
+        <v>1.9589998722076416</v>
       </c>
       <c r="J4" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -396,13 +405,13 @@
         <v>21</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>54.0</v>
+        <v>21.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>1.0</v>
+        <v>73.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>1.0</v>
+        <v>57.0</v>
       </c>
       <c r="G5" t="b" s="0">
         <v>0</v>
@@ -411,10 +420,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>9.319000244140625</v>
+        <v>0.8240000009536743</v>
       </c>
       <c r="J5" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -428,13 +437,13 @@
         <v>24</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>50.0</v>
+        <v>21.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G6" t="b" s="0">
         <v>0</v>
@@ -443,10 +452,10 @@
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>18.14699935913086</v>
+        <v>1.9960001707077026</v>
       </c>
       <c r="J6" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -460,13 +469,13 @@
         <v>27</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G7" t="b" s="0">
         <v>0</v>
@@ -475,10 +484,10 @@
         <v>1</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>0.6620000004768372</v>
+        <v>1.2990000247955322</v>
       </c>
       <c r="J7" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -492,13 +501,13 @@
         <v>30</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>18.0</v>
+        <v>12.0</v>
       </c>
       <c r="E8" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G8" t="b" s="0">
         <v>0</v>
@@ -507,10 +516,10 @@
         <v>1</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>7.554999828338623</v>
+        <v>0.6859999895095825</v>
       </c>
       <c r="J8" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -524,7 +533,7 @@
         <v>33</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>27.0</v>
+        <v>21.0</v>
       </c>
       <c r="E9" t="n" s="0">
         <v>1.0</v>
@@ -539,10 +548,10 @@
         <v>1</v>
       </c>
       <c r="I9" t="n" s="0">
-        <v>2.5989999771118164</v>
+        <v>7.270999908447266</v>
       </c>
       <c r="J9" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -553,10 +562,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>27.0</v>
+        <v>21.0</v>
       </c>
       <c r="E10" t="n" s="0">
         <v>1.0</v>
@@ -571,30 +580,30 @@
         <v>1</v>
       </c>
       <c r="I10" t="n" s="0">
-        <v>6.164000034332275</v>
+        <v>7.002999782562256</v>
       </c>
       <c r="J10" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="B11" t="s" s="0">
+      <c r="C11" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="C11" t="s" s="0">
-        <v>39</v>
-      </c>
       <c r="D11" t="n" s="0">
-        <v>57.0</v>
+        <v>21.0</v>
       </c>
       <c r="E11" t="n" s="0">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="F11" t="n" s="0">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G11" t="b" s="0">
         <v>0</v>
@@ -603,27 +612,27 @@
         <v>1</v>
       </c>
       <c r="I11" t="n" s="0">
-        <v>20.902000427246094</v>
+        <v>7.4120001792907715</v>
       </c>
       <c r="J11" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B12" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="B12" t="s" s="0">
+      <c r="C12" t="s" s="0">
         <v>41</v>
       </c>
-      <c r="C12" t="s" s="0">
-        <v>42</v>
-      </c>
       <c r="D12" t="n" s="0">
-        <v>15.0</v>
+        <v>21.0</v>
       </c>
       <c r="E12" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F12" t="n" s="0">
         <v>1.0</v>
@@ -635,15 +644,15 @@
         <v>1</v>
       </c>
       <c r="I12" t="n" s="0">
-        <v>11.237998962402344</v>
+        <v>1.0989999771118164</v>
       </c>
       <c r="J12" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s" s="0">
         <v>43</v>
@@ -652,13 +661,13 @@
         <v>44</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>18.0</v>
+        <v>31.0</v>
       </c>
       <c r="E13" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="F13" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G13" t="b" s="0">
         <v>0</v>
@@ -667,30 +676,30 @@
         <v>1</v>
       </c>
       <c r="I13" t="n" s="0">
-        <v>8.28600025177002</v>
+        <v>2.2319998741149902</v>
       </c>
       <c r="J13" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s" s="0">
         <v>45</v>
       </c>
-      <c r="B14" t="s" s="0">
+      <c r="C14" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="C14" t="s" s="0">
-        <v>47</v>
-      </c>
       <c r="D14" t="n" s="0">
-        <v>57.0</v>
+        <v>18.0</v>
       </c>
       <c r="E14" t="n" s="0">
-        <v>73.0</v>
+        <v>1.0</v>
       </c>
       <c r="F14" t="n" s="0">
-        <v>57.0</v>
+        <v>1.0</v>
       </c>
       <c r="G14" t="b" s="0">
         <v>0</v>
@@ -699,24 +708,24 @@
         <v>1</v>
       </c>
       <c r="I14" t="n" s="0">
-        <v>21.788002014160156</v>
+        <v>7.600000381469727</v>
       </c>
       <c r="J14" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s" s="0">
         <v>48</v>
       </c>
-      <c r="B15" t="s" s="0">
+      <c r="C15" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="C15" t="s" s="0">
-        <v>50</v>
-      </c>
       <c r="D15" t="n" s="0">
-        <v>57.0</v>
+        <v>21.0</v>
       </c>
       <c r="E15" t="n" s="0">
         <v>1.0</v>
@@ -731,30 +740,30 @@
         <v>1</v>
       </c>
       <c r="I15" t="n" s="0">
-        <v>23.68600082397461</v>
+        <v>1.6829999685287476</v>
       </c>
       <c r="J15" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B16" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="B16" t="s" s="0">
+      <c r="C16" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="C16" t="s" s="0">
-        <v>53</v>
-      </c>
       <c r="D16" t="n" s="0">
-        <v>50.0</v>
+        <v>31.0</v>
       </c>
       <c r="E16" t="n" s="0">
-        <v>25.0</v>
+        <v>1.0</v>
       </c>
       <c r="F16" t="n" s="0">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G16" t="b" s="0">
         <v>0</v>
@@ -763,30 +772,30 @@
         <v>1</v>
       </c>
       <c r="I16" t="n" s="0">
-        <v>36.85900115966797</v>
+        <v>3.3859996795654297</v>
       </c>
       <c r="J16" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B17" t="s" s="0">
         <v>54</v>
       </c>
-      <c r="B17" t="s" s="0">
+      <c r="C17" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="C17" t="s" s="0">
-        <v>56</v>
-      </c>
       <c r="D17" t="n" s="0">
-        <v>47.0</v>
+        <v>31.0</v>
       </c>
       <c r="E17" t="n" s="0">
-        <v>30.0</v>
+        <v>4.0</v>
       </c>
       <c r="F17" t="n" s="0">
-        <v>12.0</v>
+        <v>3.0</v>
       </c>
       <c r="G17" t="b" s="0">
         <v>0</v>
@@ -795,24 +804,24 @@
         <v>1</v>
       </c>
       <c r="I17" t="n" s="0">
-        <v>24.220001220703125</v>
+        <v>2.50600004196167</v>
       </c>
       <c r="J17" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>54.0</v>
+        <v>61.0</v>
       </c>
       <c r="E18" t="n" s="0">
         <v>1.0</v>
@@ -827,30 +836,30 @@
         <v>1</v>
       </c>
       <c r="I18" t="n" s="0">
-        <v>43.875</v>
+        <v>34.4370002746582</v>
       </c>
       <c r="J18" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="C19" t="s" s="0">
         <v>59</v>
       </c>
-      <c r="B19" t="s" s="0">
-        <v>60</v>
-      </c>
-      <c r="C19" t="s" s="0">
-        <v>61</v>
-      </c>
       <c r="D19" t="n" s="0">
-        <v>50.0</v>
+        <v>58.0</v>
       </c>
       <c r="E19" t="n" s="0">
-        <v>19.0</v>
+        <v>1.0</v>
       </c>
       <c r="F19" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G19" t="b" s="0">
         <v>0</v>
@@ -859,30 +868,30 @@
         <v>1</v>
       </c>
       <c r="I19" t="n" s="0">
-        <v>24.948999404907227</v>
+        <v>34.55400466918945</v>
       </c>
       <c r="J19" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s" s="0">
         <v>62</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
       <c r="E20" t="n" s="0">
-        <v>1.0</v>
+        <v>25.0</v>
       </c>
       <c r="F20" t="n" s="0">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G20" t="b" s="0">
         <v>0</v>
@@ -891,10 +900,10 @@
         <v>1</v>
       </c>
       <c r="I20" t="n" s="0">
-        <v>25.6720027923584</v>
+        <v>26.953001022338867</v>
       </c>
       <c r="J20" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -908,13 +917,13 @@
         <v>65</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>54.0</v>
+        <v>58.0</v>
       </c>
       <c r="E21" t="n" s="0">
-        <v>1.0</v>
+        <v>30.0</v>
       </c>
       <c r="F21" t="n" s="0">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G21" t="b" s="0">
         <v>0</v>
@@ -923,10 +932,42 @@
         <v>1</v>
       </c>
       <c r="I21" t="n" s="0">
-        <v>27.87200164794922</v>
+        <v>27.608003616333008</v>
       </c>
       <c r="J21" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="D22" t="n" s="0">
+        <v>62.0</v>
+      </c>
+      <c r="E22" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="F22" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G22" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n" s="0">
+        <v>30.058002471923828</v>
+      </c>
+      <c r="J22" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
